--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008450004899078973</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>23231438</v>
+        <v>4334444</v>
       </c>
       <c r="L2" t="n">
-        <v>13806680</v>
+        <v>2352033</v>
       </c>
       <c r="M2" t="n">
-        <v>3543788</v>
+        <v>536928</v>
       </c>
       <c r="N2" t="n">
-        <v>195394</v>
+        <v>20191</v>
       </c>
       <c r="O2" t="n">
-        <v>2097679</v>
+        <v>328902</v>
       </c>
       <c r="P2" t="n">
-        <v>817575</v>
+        <v>129762</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999849796295166</v>
+        <v>0.9999912977218628</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9200028777122498</v>
+        <v>0.8516453504562378</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8339127898216248</v>
+        <v>0.7058770060539246</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7942436337471008</v>
+        <v>0.6328914165496826</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5307888984680176</v>
+        <v>0.194640189409256</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8304811120033264</v>
+        <v>0.6854066848754883</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8898019790649414</v>
+        <v>0.7959442734718323</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026420486158906</v>
       </c>
       <c r="C3" t="n">
-        <v>365</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>23231438</v>
+        <v>4334444</v>
       </c>
       <c r="E3" t="n">
-        <v>1880472</v>
+        <v>669988</v>
       </c>
       <c r="F3" t="n">
-        <v>25811</v>
+        <v>11371</v>
       </c>
       <c r="G3" t="n">
-        <v>3087</v>
+        <v>1083</v>
       </c>
       <c r="H3" t="n">
-        <v>1308</v>
+        <v>665</v>
       </c>
       <c r="I3" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>50082636</v>
+        <v>10016567</v>
       </c>
       <c r="K3" t="n">
-        <v>54485414</v>
+        <v>10556977</v>
       </c>
       <c r="L3" t="n">
-        <v>62577000</v>
+        <v>12076134</v>
       </c>
       <c r="M3" t="n">
-        <v>76068652</v>
+        <v>15084736</v>
       </c>
       <c r="N3" t="n">
-        <v>81029627</v>
+        <v>16156798</v>
       </c>
       <c r="O3" t="n">
-        <v>78673953</v>
+        <v>15669086</v>
       </c>
       <c r="P3" t="n">
-        <v>80580162</v>
+        <v>16102940</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9239892959594727</v>
+        <v>0.8638526797294617</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8459365963935852</v>
+        <v>0.7185231447219849</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7602580785751343</v>
+        <v>0.5752272009849548</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4384501576423645</v>
+        <v>0.2262094169855118</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8239549994468689</v>
+        <v>0.6454728841781616</v>
       </c>
       <c r="W3" t="n">
-        <v>0.845838725566864</v>
+        <v>0.6709756851196289</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1911522</v>
+        <v>714899</v>
       </c>
       <c r="E4" t="n">
-        <v>13806680</v>
+        <v>2352033</v>
       </c>
       <c r="F4" t="n">
-        <v>547820</v>
+        <v>180995</v>
       </c>
       <c r="G4" t="n">
-        <v>18562</v>
+        <v>9332</v>
       </c>
       <c r="H4" t="n">
-        <v>34117</v>
+        <v>14994</v>
       </c>
       <c r="I4" t="n">
-        <v>2472</v>
+        <v>1171</v>
       </c>
       <c r="J4" t="n">
-        <v>474</v>
+        <v>55</v>
       </c>
       <c r="K4" t="n">
-        <v>2020046</v>
+        <v>755050</v>
       </c>
       <c r="L4" t="n">
-        <v>2749824</v>
+        <v>980039</v>
       </c>
       <c r="M4" t="n">
-        <v>918052</v>
+        <v>311445</v>
       </c>
       <c r="N4" t="n">
-        <v>172726</v>
+        <v>83544</v>
       </c>
       <c r="O4" t="n">
-        <v>428181</v>
+        <v>150962</v>
       </c>
       <c r="P4" t="n">
-        <v>101253</v>
+        <v>33267</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999924898147583</v>
+        <v>0.9999956488609314</v>
       </c>
       <c r="R4" t="n">
-        <v>0.921991765499115</v>
+        <v>0.8577056527137756</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8398816585540771</v>
+        <v>0.7121439576148987</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7768793702125549</v>
+        <v>0.6026830673217773</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4802210032939911</v>
+        <v>0.2092407494783401</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8272051811218262</v>
+        <v>0.6648406386375427</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8672635555267334</v>
+        <v>0.7281368374824524</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>67288</v>
+        <v>26208</v>
       </c>
       <c r="E5" t="n">
-        <v>749804</v>
+        <v>266624</v>
       </c>
       <c r="F5" t="n">
-        <v>3543788</v>
+        <v>536928</v>
       </c>
       <c r="G5" t="n">
-        <v>70355</v>
+        <v>29019</v>
       </c>
       <c r="H5" t="n">
-        <v>216308</v>
+        <v>68521</v>
       </c>
       <c r="I5" t="n">
-        <v>13748</v>
+        <v>6114</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1911102</v>
+        <v>683129</v>
       </c>
       <c r="L5" t="n">
-        <v>2514496</v>
+        <v>921394</v>
       </c>
       <c r="M5" t="n">
-        <v>1117508</v>
+        <v>396491</v>
       </c>
       <c r="N5" t="n">
-        <v>250253</v>
+        <v>69067</v>
       </c>
       <c r="O5" t="n">
-        <v>448187</v>
+        <v>180650</v>
       </c>
       <c r="P5" t="n">
-        <v>149010</v>
+        <v>63631</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999966025352478</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9518525004386902</v>
+        <v>0.911928117275238</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9355242252349854</v>
+        <v>0.8835591077804565</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9750691056251526</v>
+        <v>0.9566470980644226</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9948194622993469</v>
+        <v>0.9906543493270874</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9892665147781372</v>
+        <v>0.9796925783157349</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9969348311424255</v>
+        <v>0.9940661191940308</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>40744</v>
+        <v>13579</v>
       </c>
       <c r="E6" t="n">
-        <v>76360</v>
+        <v>19678</v>
       </c>
       <c r="F6" t="n">
-        <v>88421</v>
+        <v>24181</v>
       </c>
       <c r="G6" t="n">
-        <v>195394</v>
+        <v>20191</v>
       </c>
       <c r="H6" t="n">
-        <v>41544</v>
+        <v>10618</v>
       </c>
       <c r="I6" t="n">
-        <v>3147</v>
+        <v>1001</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="E7" t="n">
-        <v>41115</v>
+        <v>22624</v>
       </c>
       <c r="F7" t="n">
-        <v>247885</v>
+        <v>90813</v>
       </c>
       <c r="G7" t="n">
-        <v>76946</v>
+        <v>41909</v>
       </c>
       <c r="H7" t="n">
-        <v>2097679</v>
+        <v>328902</v>
       </c>
       <c r="I7" t="n">
-        <v>81827</v>
+        <v>24962</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>2073</v>
+        <v>1125</v>
       </c>
       <c r="F8" t="n">
-        <v>8115</v>
+        <v>4085</v>
       </c>
       <c r="G8" t="n">
-        <v>3776</v>
+        <v>2201</v>
       </c>
       <c r="H8" t="n">
-        <v>134904</v>
+        <v>56164</v>
       </c>
       <c r="I8" t="n">
-        <v>817575</v>
+        <v>129762</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
